--- a/src/test/resources/TestData/data.xlsx
+++ b/src/test/resources/TestData/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Course\Selenium_Java\SeleniumNov25\Nov25Cucumber\src\test\resources\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1323D691-314E-463F-B1EB-16F7D6DBE47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2948D39-D6C7-471F-9E94-7785FEBB77D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -73,6 +73,39 @@
   </si>
   <si>
     <t>Multi_lead_creation_TC05</t>
+  </si>
+  <si>
+    <t>Get_All_Employee_TC06</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>/api/v1/employees</t>
+  </si>
+  <si>
+    <t>Get_Employee_TC07</t>
+  </si>
+  <si>
+    <t>/api/v1/employee/1</t>
+  </si>
+  <si>
+    <t>/api/v1/create</t>
+  </si>
+  <si>
+    <t>Create_Employee_TC08</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>Darshan</t>
   </si>
 </sst>
 </file>
@@ -148,11 +181,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,13 +467,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36.73046875" customWidth="1"/>
+    <col min="7" max="7" width="20.73046875" customWidth="1"/>
+    <col min="9" max="9" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,8 +494,20 @@
       <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -473,7 +521,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -487,7 +535,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -507,7 +555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -516,6 +564,39 @@
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8">
+        <v>2352572528</v>
+      </c>
+      <c r="J8">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
